--- a/data/trans_dic/P22$ss-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$ss-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguridad Social</t>
+          <t>Población que, al menos, es beneficiaria de la Seguridad Social (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>97,06; 98,76</t>
+          <t>96,91; 98,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>97,49; 99,19</t>
+          <t>97,24; 99,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,7; 99,44</t>
+          <t>97,72; 99,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98,13; 99,67</t>
+          <t>98,02; 99,67</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,76; 97,69</t>
+          <t>95,83; 97,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,62; 99,09</t>
+          <t>97,65; 99,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,09; 99,47</t>
+          <t>97,96; 99,52</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>98,29; 99,45</t>
+          <t>98,26; 99,45</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>96,62; 97,98</t>
+          <t>96,68; 98,06</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97,85; 98,92</t>
+          <t>97,91; 98,97</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98,3; 99,35</t>
+          <t>98,23; 99,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,53; 99,44</t>
+          <t>98,55; 99,45</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>96,01; 97,76</t>
+          <t>95,94; 97,74</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,76; 96,74</t>
+          <t>94,84; 96,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,39; 97,16</t>
+          <t>95,38; 97,14</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96,07; 98,12</t>
+          <t>96,04; 98,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,97; 96,93</t>
+          <t>94,95; 96,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,24; 97,24</t>
+          <t>95,23; 97,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,56; 98,06</t>
+          <t>96,51; 98,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>97,43; 98,71</t>
+          <t>97,4; 98,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95,76; 97,07</t>
+          <t>95,82; 97,13</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95,27; 96,75</t>
+          <t>95,27; 96,77</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96,18; 97,36</t>
+          <t>96,19; 97,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>97,0; 98,16</t>
+          <t>97,02; 98,19</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,23; 90,25</t>
+          <t>84,73; 90,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,43; 89,64</t>
+          <t>82,19; 89,37</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,13; 88,42</t>
+          <t>82,01; 88,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,35; 94,26</t>
+          <t>90,4; 94,41</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,86; 92,37</t>
+          <t>86,58; 92,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,26; 92,58</t>
+          <t>86,48; 92,54</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,74; 91,12</t>
+          <t>85,62; 91,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,14; 93,02</t>
+          <t>89,54; 93,12</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,64; 90,63</t>
+          <t>86,26; 90,48</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,49; 90,2</t>
+          <t>85,27; 90,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>85,03; 89,22</t>
+          <t>84,83; 89,07</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90,62; 93,17</t>
+          <t>90,56; 93,33</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>94,93; 96,41</t>
+          <t>95,02; 96,43</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,33; 95,98</t>
+          <t>94,4; 96,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,3; 95,87</t>
+          <t>94,35; 95,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95,8; 97,37</t>
+          <t>95,74; 97,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,72; 96,16</t>
+          <t>94,67; 96,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,63; 96,97</t>
+          <t>95,56; 96,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,8; 97,08</t>
+          <t>95,77; 97,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>96,51; 97,66</t>
+          <t>96,5; 97,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,06; 96,09</t>
+          <t>95,01; 96,03</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95,27; 96,34</t>
+          <t>95,26; 96,31</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95,28; 96,27</t>
+          <t>95,28; 96,28</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,35; 97,34</t>
+          <t>96,29; 97,3</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menor, es beneficiaria de Seguridad Social</t>
+          <t>Población que, al menos, es beneficiaria de la Seguridad Social (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>998664; 1016151</t>
+          <t>997092; 1015533</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>950167; 966758</t>
+          <t>947717; 965921</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>735827; 748962</t>
+          <t>735975; 748526</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>505298; 513247</t>
+          <t>504722; 513252</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1258525; 1283935</t>
+          <t>1259493; 1284181</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1305952; 1325611</t>
+          <t>1306330; 1325719</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>971826; 985507</t>
+          <t>970493; 985925</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>740273; 749054</t>
+          <t>740051; 749005</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2264062; 2295719</t>
+          <t>2265324; 2297637</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2262690; 2287381</t>
+          <t>2264026; 2288715</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1714208; 1732600</t>
+          <t>1712992; 1731771</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1249500; 1260971</t>
+          <t>1249718; 1261143</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1622478; 1651991</t>
+          <t>1621171; 1651680</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1860087; 1899072</t>
+          <t>1861706; 1901351</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1978076; 2014692</t>
+          <t>1977743; 2014372</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2200238; 2247250</t>
+          <t>2199707; 2245441</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1506697; 1537760</t>
+          <t>1506369; 1538464</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1674110; 1709284</t>
+          <t>1674012; 1709786</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1918147; 1947972</t>
+          <t>1917139; 1948379</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2180160; 2208816</t>
+          <t>2179580; 2207726</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3137284; 3180498</t>
+          <t>3139273; 3182450</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3544661; 3599668</t>
+          <t>3544838; 3600428</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3905088; 3952750</t>
+          <t>3905326; 3953805</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4392250; 4444673</t>
+          <t>4392962; 4446000</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>464441; 497632</t>
+          <t>467191; 498479</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>396622; 431328</t>
+          <t>395476; 430026</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>448393; 482724</t>
+          <t>447737; 481742</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>584245; 609530</t>
+          <t>584547; 610490</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>413798; 440074</t>
+          <t>412455; 438432</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>395598; 424610</t>
+          <t>396633; 424426</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>470818; 500384</t>
+          <t>470157; 501410</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>588729; 614368</t>
+          <t>591358; 615043</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>890502; 931473</t>
+          <t>886634; 930011</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>803451; 847721</t>
+          <t>801339; 848323</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>931089; 977021</t>
+          <t>928936; 975399</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1184442; 1217767</t>
+          <t>1183743; 1219968</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3104184; 3152618</t>
+          <t>3107381; 3153465</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3224960; 3281431</t>
+          <t>3227396; 3284408</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3180292; 3233513</t>
+          <t>3182211; 3234759</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3306877; 3360946</t>
+          <t>3304774; 3361736</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3198770; 3247499</t>
+          <t>3197097; 3246151</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3399066; 3446696</t>
+          <t>3396556; 3446242</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3378330; 3423437</t>
+          <t>3377150; 3423330</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3523944; 3565693</t>
+          <t>3523591; 3565463</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6319080; 6387327</t>
+          <t>6315493; 6383131</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6643483; 6718075</t>
+          <t>6642488; 6716043</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6573367; 6641623</t>
+          <t>6573434; 6642594</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6843792; 6914412</t>
+          <t>6839687; 6911260</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P22$ss-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P22$ss-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,99%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>96,91; 98,7</t>
+          <t>96,95; 98,79</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>97,24; 99,11</t>
+          <t>97,46; 99,09</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97,72; 99,38</t>
+          <t>97,82; 99,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>98,02; 99,67</t>
+          <t>98,01; 99,66</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>95,83; 97,71</t>
+          <t>95,6; 97,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,65; 99,1</t>
+          <t>97,69; 99,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,96; 99,52</t>
+          <t>98,13; 99,5</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>98,26; 99,45</t>
+          <t>98,2; 99,4</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>96,68; 98,06</t>
+          <t>96,67; 98,0</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97,91; 98,97</t>
+          <t>97,87; 98,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>98,23; 99,31</t>
+          <t>98,29; 99,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,55; 99,45</t>
+          <t>98,44; 99,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,29%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>95,94; 97,74</t>
+          <t>95,99; 97,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>94,84; 96,86</t>
+          <t>94,8; 96,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>95,38; 97,14</t>
+          <t>95,36; 97,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>96,04; 98,04</t>
+          <t>95,67; 97,51</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>94,95; 96,97</t>
+          <t>94,92; 96,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>95,23; 97,27</t>
+          <t>95,23; 97,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>96,51; 98,08</t>
+          <t>96,62; 98,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>97,4; 98,66</t>
+          <t>97,19; 98,38</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>95,82; 97,13</t>
+          <t>95,82; 97,15</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95,27; 96,77</t>
+          <t>95,33; 96,75</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96,19; 97,38</t>
+          <t>96,26; 97,38</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>97,02; 98,19</t>
+          <t>96,68; 97,76</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>84,73; 90,4</t>
+          <t>84,76; 90,17</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>82,19; 89,37</t>
+          <t>81,92; 89,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82,01; 88,24</t>
+          <t>82,02; 88,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>90,4; 94,41</t>
+          <t>90,02; 94,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>86,58; 92,03</t>
+          <t>86,72; 92,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>86,48; 92,54</t>
+          <t>86,53; 92,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>85,62; 91,31</t>
+          <t>85,81; 91,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>89,54; 93,12</t>
+          <t>89,91; 93,45</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>86,26; 90,48</t>
+          <t>86,53; 90,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,27; 90,27</t>
+          <t>85,61; 90,27</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>84,83; 89,07</t>
+          <t>84,84; 89,11</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>90,56; 93,33</t>
+          <t>90,65; 93,26</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>97,1%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,58%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>95,02; 96,43</t>
+          <t>95,01; 96,37</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>94,4; 96,07</t>
+          <t>94,41; 96,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94,35; 95,91</t>
+          <t>94,3; 95,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95,74; 97,39</t>
+          <t>95,36; 96,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,67; 96,12</t>
+          <t>94,7; 96,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,56; 96,96</t>
+          <t>95,61; 96,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,77; 97,08</t>
+          <t>95,75; 97,11</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>96,5; 97,65</t>
+          <t>96,41; 97,39</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>95,01; 96,03</t>
+          <t>95,04; 96,13</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95,26; 96,31</t>
+          <t>95,29; 96,34</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>95,28; 96,28</t>
+          <t>95,28; 96,25</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>96,29; 97,3</t>
+          <t>96,11; 96,97</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>510320</t>
+          <t>573278</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>745809</t>
+          <t>812983</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1256130</t>
+          <t>1386262</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>997092; 1015533</t>
+          <t>997522; 1016472</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>947717; 965921</t>
+          <t>949889; 965821</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>735975; 748526</t>
+          <t>736760; 749226</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>504722; 513252</t>
+          <t>567037; 576582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1259493; 1284181</t>
+          <t>1256458; 1283772</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1306330; 1325719</t>
+          <t>1306880; 1325841</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>970493; 985925</t>
+          <t>972192; 985773</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>740051; 749005</t>
+          <t>806569; 816394</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2265324; 2297637</t>
+          <t>2265230; 2296294</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>2264026; 2288715</t>
+          <t>2263132; 2288037</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1712992; 1731771</t>
+          <t>1713988; 1732651</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1249718; 1261143</t>
+          <t>1378040; 1391253</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2223527</t>
+          <t>2156682</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2195694</t>
+          <t>2124845</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4419221</t>
+          <t>4281527</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1621171; 1651680</t>
+          <t>1622141; 1652043</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1861706; 1901351</t>
+          <t>1860825; 1899516</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1977743; 2014372</t>
+          <t>1977489; 2015540</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2199707; 2245441</t>
+          <t>2134091; 2174926</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1506369; 1538464</t>
+          <t>1505968; 1538176</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1674012; 1709786</t>
+          <t>1674023; 1709056</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1917139; 1948379</t>
+          <t>1919328; 1948361</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2179580; 2207726</t>
+          <t>2109263; 2135223</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3139273; 3182450</t>
+          <t>3139459; 3182824</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3544838; 3600428</t>
+          <t>3547128; 3599953</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3905326; 3953805</t>
+          <t>3908305; 3953559</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4392962; 4446000</t>
+          <t>4254887; 4302186</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>599090</t>
+          <t>656153</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>603906</t>
+          <t>675110</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1202996</t>
+          <t>1331264</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>467191; 498479</t>
+          <t>467399; 497194</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>395476; 430026</t>
+          <t>394183; 429212</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>447737; 481742</t>
+          <t>447766; 483035</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>584547; 610490</t>
+          <t>640591; 669380</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>412455; 438432</t>
+          <t>413127; 439709</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>396633; 424426</t>
+          <t>396849; 425650</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>470157; 501410</t>
+          <t>471196; 501200</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>591358; 615043</t>
+          <t>660701; 686724</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>886634; 930011</t>
+          <t>889338; 930645</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>801339; 848323</t>
+          <t>804602; 848327</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>928936; 975399</t>
+          <t>929007; 975857</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1183743; 1219968</t>
+          <t>1311291; 1348985</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3332938</t>
+          <t>3386114</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>3545409</t>
+          <t>3612939</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6878347</t>
+          <t>6999052</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3107381; 3153465</t>
+          <t>3106908; 3151417</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>3227396; 3284408</t>
+          <t>3227565; 3282456</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3182211; 3234759</t>
+          <t>3180355; 3233473</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3304774; 3361736</t>
+          <t>3357406; 3408982</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3197097; 3246151</t>
+          <t>3198295; 3247317</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3396556; 3446242</t>
+          <t>3398247; 3444752</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3377150; 3423330</t>
+          <t>3376285; 3424508</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3523591; 3565463</t>
+          <t>3592560; 3629348</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6315493; 6383131</t>
+          <t>6317930; 6390272</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>6642488; 6716043</t>
+          <t>6644646; 6718066</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6573434; 6642594</t>
+          <t>6573534; 6640102</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6839687; 6911260</t>
+          <t>6965212; 7027870</t>
         </is>
       </c>
     </row>
